--- a/input/作品情報フォーム.xlsx
+++ b/input/作品情報フォーム.xlsx
@@ -5,19 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ka5ry\Documents\work\kushodo_brochure_gen\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ka5ry\Documents\work\kushodo_brochure_gen\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{79139C28-460F-4EC8-B9EA-1A09B35F1706}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CB7F691-BC64-457A-9500-AC5C325E08F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="個人" sheetId="2" r:id="rId1"/>
     <sheet name="合作" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -899,22 +898,6 @@
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="16">
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF5B3F86"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF5B3F86"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF5B3F86"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF5B3F86"/>
-        </bottom>
-      </border>
-    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1059,31 +1042,47 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF5B3F86"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF5B3F86"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF5B3F86"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF5B3F86"/>
+        </bottom>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="4">
     <tableStyle name="第二回個人-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="12"/>
-      <tableStyleElement type="headerRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="secondRowStripe" dxfId="13"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="15"/>
+      <tableStyleElement type="headerRow" dxfId="14"/>
+      <tableStyleElement type="firstRowStripe" dxfId="13"/>
+      <tableStyleElement type="secondRowStripe" dxfId="12"/>
     </tableStyle>
     <tableStyle name="第二回合作-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="8"/>
-      <tableStyleElement type="headerRow" dxfId="11"/>
-      <tableStyleElement type="firstRowStripe" dxfId="10"/>
-      <tableStyleElement type="secondRowStripe" dxfId="9"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="11"/>
+      <tableStyleElement type="headerRow" dxfId="10"/>
+      <tableStyleElement type="firstRowStripe" dxfId="9"/>
+      <tableStyleElement type="secondRowStripe" dxfId="8"/>
     </tableStyle>
     <tableStyle name="フォームの回答 1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF02000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="4"/>
-      <tableStyleElement type="headerRow" dxfId="7"/>
-      <tableStyleElement type="firstRowStripe" dxfId="6"/>
-      <tableStyleElement type="secondRowStripe" dxfId="5"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="6"/>
+      <tableStyleElement type="firstRowStripe" dxfId="5"/>
+      <tableStyleElement type="secondRowStripe" dxfId="4"/>
     </tableStyle>
     <tableStyle name="フォームの回答 2-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF03000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="0"/>
-      <tableStyleElement type="headerRow" dxfId="3"/>
-      <tableStyleElement type="firstRowStripe" dxfId="2"/>
-      <tableStyleElement type="secondRowStripe" dxfId="1"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="3"/>
+      <tableStyleElement type="headerRow" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="secondRowStripe" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <extLst>

--- a/input/作品情報フォーム.xlsx
+++ b/input/作品情報フォーム.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ka5ry\Documents\work\kushodo_brochure_gen\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CB7F691-BC64-457A-9500-AC5C325E08F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9EB1F6F-2C5B-453C-A8A9-4F414BD7866F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="17280" windowHeight="10665" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="個人" sheetId="2" r:id="rId1"/>
